--- a/data_in/all_height_data.xlsx
+++ b/data_in/all_height_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksonstrand/Documents/GitHub/Linaria_specProj/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksonstrand/Documents/GitHub/Linaria_specProj/data_in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3292A9-F21C-C242-A0C8-499AB893419F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BAE643-D873-8E42-94FA-BB86B57D4BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
+    <workbookView xWindow="4080" yWindow="1600" windowWidth="30240" windowHeight="18980" activeTab="8" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
   </bookViews>
   <sheets>
     <sheet name="D1 3 2 26" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,9 @@
     <sheet name="check" sheetId="4" r:id="rId4"/>
     <sheet name="D4 3 16 26" sheetId="5" r:id="rId5"/>
     <sheet name="D5 3 23 26" sheetId="6" r:id="rId6"/>
-    <sheet name="meta_data" sheetId="8" r:id="rId7"/>
+    <sheet name="D6 4 6 26" sheetId="9" r:id="rId7"/>
+    <sheet name="meta_data" sheetId="8" r:id="rId8"/>
+    <sheet name="weights" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="102">
   <si>
     <t>lc1</t>
   </si>
@@ -324,6 +326,30 @@
   </si>
   <si>
     <t>tophalf</t>
+  </si>
+  <si>
+    <t>main stem dry and dying</t>
+  </si>
+  <si>
+    <t>aphids on top</t>
+  </si>
+  <si>
+    <t>really bad aphids</t>
+  </si>
+  <si>
+    <t>plant</t>
+  </si>
+  <si>
+    <t>wet_main</t>
+  </si>
+  <si>
+    <t>wet_side</t>
+  </si>
+  <si>
+    <t>dry_main</t>
+  </si>
+  <si>
+    <t>dry_side</t>
   </si>
 </sst>
 </file>
@@ -433,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -475,11 +501,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2822,7 +2882,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE5FBDB2-05DA-4147-86EE-87FF8AF99D12}">
-  <dimension ref="A1:W42"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="19" width="4.5" customWidth="1"/>
@@ -2927,10 +2987,19 @@
         <v>46090</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>7.5</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="D3">
+        <v>2.7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4.5</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
@@ -2938,19 +3007,13 @@
         <v>46090</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>8.3000000000000007</v>
+        <v>32.1</v>
       </c>
       <c r="D4">
-        <v>2.7</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
@@ -2958,13 +3021,16 @@
         <v>46090</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>32.1</v>
+        <v>49.2</v>
       </c>
       <c r="D5">
-        <v>1.2</v>
+        <v>14.7</v>
+      </c>
+      <c r="T5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
@@ -2972,16 +3038,28 @@
         <v>46090</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>49.2</v>
+        <v>40.9</v>
       </c>
       <c r="D6">
-        <v>14.7</v>
+        <v>32.200000000000003</v>
+      </c>
+      <c r="E6">
+        <v>29.1</v>
+      </c>
+      <c r="F6">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G6">
+        <v>3.2</v>
+      </c>
+      <c r="H6">
+        <v>2.4</v>
       </c>
       <c r="T6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
@@ -2989,28 +3067,13 @@
         <v>46090</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C7">
-        <v>40.9</v>
-      </c>
-      <c r="D7">
-        <v>32.200000000000003</v>
-      </c>
-      <c r="E7">
-        <v>29.1</v>
-      </c>
-      <c r="F7">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="G7">
-        <v>3.2</v>
-      </c>
-      <c r="H7">
-        <v>2.4</v>
+        <v>31.1</v>
       </c>
       <c r="T7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -3018,13 +3081,28 @@
         <v>46090</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>31.1</v>
-      </c>
-      <c r="T8" t="s">
-        <v>72</v>
+        <v>8.5</v>
+      </c>
+      <c r="D8">
+        <v>27.6</v>
+      </c>
+      <c r="E8">
+        <v>29.1</v>
+      </c>
+      <c r="F8">
+        <v>26.5</v>
+      </c>
+      <c r="G8">
+        <v>24.5</v>
+      </c>
+      <c r="H8">
+        <v>5.4</v>
+      </c>
+      <c r="I8">
+        <v>6.1</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
@@ -3032,28 +3110,34 @@
         <v>46090</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C9">
-        <v>8.5</v>
+        <f>45+21.7</f>
+        <v>66.7</v>
       </c>
       <c r="D9">
-        <v>27.6</v>
+        <v>37</v>
       </c>
       <c r="E9">
-        <v>29.1</v>
+        <v>5.6</v>
       </c>
       <c r="F9">
-        <v>26.5</v>
+        <v>4.3</v>
       </c>
       <c r="G9">
-        <v>24.5</v>
+        <v>34.4</v>
       </c>
       <c r="H9">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="I9">
-        <v>6.1</v>
+        <f>45+9.2</f>
+        <v>54.2</v>
+      </c>
+      <c r="J9">
+        <f>45+11.8</f>
+        <v>56.8</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
@@ -3061,34 +3145,14 @@
         <v>46090</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <f>45+21.7</f>
-        <v>66.7</v>
+        <f>45+7.1</f>
+        <v>52.1</v>
       </c>
       <c r="D10">
-        <v>37</v>
-      </c>
-      <c r="E10">
-        <v>5.6</v>
-      </c>
-      <c r="F10">
-        <v>4.3</v>
-      </c>
-      <c r="G10">
-        <v>34.4</v>
-      </c>
-      <c r="H10">
-        <v>16.5</v>
-      </c>
-      <c r="I10">
-        <f>45+9.2</f>
-        <v>54.2</v>
-      </c>
-      <c r="J10">
-        <f>45+11.8</f>
-        <v>56.8</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
@@ -3096,14 +3160,28 @@
         <v>46090</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <f>45+7.1</f>
-        <v>52.1</v>
+        <v>8.6</v>
       </c>
       <c r="D11">
-        <v>20.6</v>
+        <v>7.6</v>
+      </c>
+      <c r="E11">
+        <v>8.1</v>
+      </c>
+      <c r="F11">
+        <v>11.2</v>
+      </c>
+      <c r="G11">
+        <v>28.2</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>1.4</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
@@ -3111,28 +3189,37 @@
         <v>46090</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C12">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="D12">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="E12">
-        <v>8.1</v>
+        <v>2.6</v>
       </c>
       <c r="F12">
-        <v>11.2</v>
+        <v>3.2</v>
       </c>
       <c r="G12">
-        <v>28.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>1.4</v>
+        <v>26.4</v>
+      </c>
+      <c r="U12">
+        <v>5.6</v>
+      </c>
+      <c r="V12">
+        <v>2.9</v>
+      </c>
+      <c r="W12">
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
@@ -3140,37 +3227,10 @@
         <v>46090</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C13">
-        <v>7.6</v>
-      </c>
-      <c r="D13">
-        <v>19.5</v>
-      </c>
-      <c r="E13">
-        <v>2.6</v>
-      </c>
-      <c r="F13">
-        <v>3.2</v>
-      </c>
-      <c r="G13">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H13">
-        <v>3</v>
-      </c>
-      <c r="I13">
-        <v>26.4</v>
-      </c>
-      <c r="U13">
-        <v>5.6</v>
-      </c>
-      <c r="V13">
-        <v>2.9</v>
-      </c>
-      <c r="W13">
-        <v>2.2999999999999998</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
@@ -3178,10 +3238,19 @@
         <v>46090</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C14">
-        <v>36.1</v>
+        <v>24.1</v>
+      </c>
+      <c r="D14">
+        <v>9.6</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+      <c r="F14">
+        <v>27.1</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
@@ -3189,19 +3258,16 @@
         <v>46090</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C15">
-        <v>24.1</v>
+        <v>19</v>
       </c>
       <c r="D15">
-        <v>9.6</v>
+        <v>15.4</v>
       </c>
       <c r="E15">
-        <v>20</v>
-      </c>
-      <c r="F15">
-        <v>27.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
@@ -3209,16 +3275,17 @@
         <v>46090</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D16">
-        <v>15.4</v>
+        <v>1.6</v>
       </c>
       <c r="E16">
-        <v>1.2</v>
+        <f>45+13.8</f>
+        <v>58.8</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.2">
@@ -3226,17 +3293,25 @@
         <v>46090</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C17">
-        <v>9</v>
+        <v>35.6</v>
       </c>
       <c r="D17">
-        <v>1.6</v>
+        <v>12.2</v>
       </c>
       <c r="E17">
-        <f>45+13.8</f>
-        <v>58.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="F17">
+        <v>4.8</v>
+      </c>
+      <c r="G17">
+        <v>5.6</v>
+      </c>
+      <c r="H17">
+        <v>7.6</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.2">
@@ -3244,25 +3319,22 @@
         <v>46090</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>35.6</v>
+        <v>45</v>
       </c>
       <c r="D18">
-        <v>12.2</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="E18">
-        <v>2.6</v>
+        <v>15.1</v>
       </c>
       <c r="F18">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>5.6</v>
-      </c>
-      <c r="H18">
-        <v>7.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.2">
@@ -3270,22 +3342,25 @@
         <v>46090</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C19">
-        <v>45</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="D19">
-        <v>39.299999999999997</v>
+        <v>12.2</v>
       </c>
       <c r="E19">
-        <v>15.1</v>
+        <v>12.4</v>
       </c>
       <c r="F19">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="H19">
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.2">
@@ -3293,25 +3368,22 @@
         <v>46090</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C20">
-        <v>33.200000000000003</v>
+        <v>10.1</v>
       </c>
       <c r="D20">
-        <v>12.2</v>
+        <v>36.1</v>
       </c>
       <c r="E20">
-        <v>12.4</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F20">
-        <v>4.7</v>
+        <v>45.4</v>
       </c>
       <c r="G20">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="H20">
-        <v>8.3000000000000007</v>
+        <v>36.700000000000003</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.2">
@@ -3319,22 +3391,22 @@
         <v>46090</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C21">
-        <v>10.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="D21">
-        <v>36.1</v>
+        <v>11.2</v>
       </c>
       <c r="E21">
-        <v>4.5999999999999996</v>
+        <v>12.6</v>
       </c>
       <c r="F21">
-        <v>45.4</v>
+        <v>15.5</v>
       </c>
       <c r="G21">
-        <v>36.700000000000003</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.2">
@@ -3342,22 +3414,16 @@
         <v>46090</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C22">
-        <v>8.1999999999999993</v>
+        <v>8.1</v>
       </c>
       <c r="D22">
-        <v>11.2</v>
+        <v>3.1</v>
       </c>
       <c r="E22">
-        <v>12.6</v>
-      </c>
-      <c r="F22">
-        <v>15.5</v>
-      </c>
-      <c r="G22">
-        <v>20.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.2">
@@ -3365,16 +3431,13 @@
         <v>46090</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C23">
-        <v>8.1</v>
-      </c>
-      <c r="D23">
-        <v>3.1</v>
-      </c>
-      <c r="E23">
-        <v>2.9</v>
+        <v>24.1</v>
+      </c>
+      <c r="T23" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.2">
@@ -3382,13 +3445,46 @@
         <v>46090</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C24">
-        <v>24.1</v>
-      </c>
-      <c r="T24" t="s">
-        <v>75</v>
+        <v>9.6</v>
+      </c>
+      <c r="D24">
+        <v>13</v>
+      </c>
+      <c r="E24">
+        <v>8</v>
+      </c>
+      <c r="F24">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G24">
+        <v>21.3</v>
+      </c>
+      <c r="H24">
+        <v>5</v>
+      </c>
+      <c r="I24">
+        <v>1.5</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>22.4</v>
+      </c>
+      <c r="L24">
+        <v>6.6</v>
+      </c>
+      <c r="M24">
+        <v>0.6</v>
+      </c>
+      <c r="N24">
+        <v>0.4</v>
+      </c>
+      <c r="O24">
+        <v>23.4</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.2">
@@ -3396,46 +3492,10 @@
         <v>46090</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C25">
-        <v>9.6</v>
-      </c>
-      <c r="D25">
-        <v>13</v>
-      </c>
-      <c r="E25">
-        <v>8</v>
-      </c>
-      <c r="F25">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="G25">
-        <v>21.3</v>
-      </c>
-      <c r="H25">
-        <v>5</v>
-      </c>
-      <c r="I25">
-        <v>1.5</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25">
-        <v>22.4</v>
-      </c>
-      <c r="L25">
-        <v>6.6</v>
-      </c>
-      <c r="M25">
-        <v>0.6</v>
-      </c>
-      <c r="N25">
-        <v>0.4</v>
-      </c>
-      <c r="O25">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.2">
@@ -3443,10 +3503,16 @@
         <v>46090</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C26">
-        <v>22.3</v>
+        <v>37.6</v>
+      </c>
+      <c r="D26">
+        <v>10.6</v>
+      </c>
+      <c r="E26">
+        <v>10.9</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.2">
@@ -3454,16 +3520,40 @@
         <v>46090</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C27">
-        <v>37.6</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D27">
-        <v>10.6</v>
+        <v>12.9</v>
       </c>
       <c r="E27">
-        <v>10.9</v>
+        <v>9.1</v>
+      </c>
+      <c r="F27">
+        <v>3.1</v>
+      </c>
+      <c r="G27">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="H27">
+        <v>6.3</v>
+      </c>
+      <c r="I27">
+        <v>4.5</v>
+      </c>
+      <c r="J27">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="K27">
+        <v>5.4</v>
+      </c>
+      <c r="L27">
+        <v>2.4</v>
+      </c>
+      <c r="M27">
+        <v>3.4</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.2">
@@ -3471,40 +3561,31 @@
         <v>46090</v>
       </c>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C28">
-        <v>9.1999999999999993</v>
+        <v>32.6</v>
       </c>
       <c r="D28">
-        <v>12.9</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="E28">
-        <v>9.1</v>
+        <v>26.1</v>
       </c>
       <c r="F28">
-        <v>3.1</v>
+        <v>28.7</v>
       </c>
       <c r="G28">
-        <v>8.3000000000000007</v>
+        <v>36</v>
       </c>
       <c r="H28">
-        <v>6.3</v>
+        <v>33.5</v>
       </c>
       <c r="I28">
-        <v>4.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J28">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="K28">
-        <v>5.4</v>
-      </c>
-      <c r="L28">
         <v>2.4</v>
-      </c>
-      <c r="M28">
-        <v>3.4</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.2">
@@ -3512,31 +3593,43 @@
         <v>46090</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C29">
-        <v>32.6</v>
+        <v>37</v>
       </c>
       <c r="D29">
-        <v>32.700000000000003</v>
+        <v>24.8</v>
       </c>
       <c r="E29">
-        <v>26.1</v>
+        <v>21.6</v>
       </c>
       <c r="F29">
-        <v>28.7</v>
+        <v>23.2</v>
       </c>
       <c r="G29">
-        <v>36</v>
+        <v>23.6</v>
       </c>
       <c r="H29">
-        <v>33.5</v>
+        <v>6.2</v>
       </c>
       <c r="I29">
-        <v>1.1000000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="J29">
-        <v>2.4</v>
+        <v>13.5</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>20.2</v>
+      </c>
+      <c r="M29">
+        <v>7</v>
+      </c>
+      <c r="N29">
+        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.2">
@@ -3544,43 +3637,28 @@
         <v>46090</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30">
+        <v>49.6</v>
+      </c>
+      <c r="D30">
+        <v>12.3</v>
+      </c>
+      <c r="E30">
+        <v>2.6</v>
+      </c>
+      <c r="F30">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="G30">
+        <v>24.9</v>
+      </c>
+      <c r="H30">
+        <v>25.7</v>
+      </c>
+      <c r="I30">
         <v>37</v>
-      </c>
-      <c r="D30">
-        <v>24.8</v>
-      </c>
-      <c r="E30">
-        <v>21.6</v>
-      </c>
-      <c r="F30">
-        <v>23.2</v>
-      </c>
-      <c r="G30">
-        <v>23.6</v>
-      </c>
-      <c r="H30">
-        <v>6.2</v>
-      </c>
-      <c r="I30">
-        <v>3.5</v>
-      </c>
-      <c r="J30">
-        <v>13.5</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="L30">
-        <v>20.2</v>
-      </c>
-      <c r="M30">
-        <v>7</v>
-      </c>
-      <c r="N30">
-        <v>9.1999999999999993</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.2">
@@ -3588,28 +3666,52 @@
         <v>46090</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C31">
-        <v>49.6</v>
+        <v>25.9</v>
       </c>
       <c r="D31">
-        <v>12.3</v>
+        <v>22.8</v>
       </c>
       <c r="E31">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>19.399999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G31">
-        <v>24.9</v>
+        <v>1.6</v>
       </c>
       <c r="H31">
-        <v>25.7</v>
+        <v>0.7</v>
       </c>
       <c r="I31">
-        <v>37</v>
+        <v>3</v>
+      </c>
+      <c r="J31">
+        <v>6</v>
+      </c>
+      <c r="K31">
+        <v>14.6</v>
+      </c>
+      <c r="L31">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="M31">
+        <v>7.2</v>
+      </c>
+      <c r="N31">
+        <v>6.2</v>
+      </c>
+      <c r="O31">
+        <v>5.8</v>
+      </c>
+      <c r="P31">
+        <v>5.9</v>
+      </c>
+      <c r="Q31">
+        <v>3.8</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.2">
@@ -3617,52 +3719,40 @@
         <v>46090</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>25.9</v>
+        <v>44.2</v>
       </c>
       <c r="D32">
-        <v>22.8</v>
+        <v>47</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>45.4</v>
       </c>
       <c r="F32">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="G32">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="H32">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="K32">
-        <v>14.6</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>5.0999999999999996</v>
+        <v>2.4</v>
       </c>
       <c r="M32">
-        <v>7.2</v>
-      </c>
-      <c r="N32">
-        <v>6.2</v>
-      </c>
-      <c r="O32">
-        <v>5.8</v>
-      </c>
-      <c r="P32">
-        <v>5.9</v>
-      </c>
-      <c r="Q32">
-        <v>3.8</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
@@ -3670,40 +3760,46 @@
         <v>46090</v>
       </c>
       <c r="B33" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C33">
-        <v>44.2</v>
+        <v>37.5</v>
       </c>
       <c r="D33">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="E33">
-        <v>45.4</v>
+        <v>11.4</v>
       </c>
       <c r="F33">
-        <v>9.4</v>
+        <v>11.2</v>
       </c>
       <c r="G33">
-        <v>3.2</v>
+        <v>17.2</v>
       </c>
       <c r="H33">
-        <v>5.4</v>
+        <v>12.2</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>22.9</v>
       </c>
       <c r="J33">
-        <v>6.6</v>
+        <v>20.5</v>
       </c>
       <c r="K33">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L33">
-        <v>2.4</v>
+        <v>15.5</v>
       </c>
       <c r="M33">
-        <v>45.6</v>
+        <v>23.9</v>
+      </c>
+      <c r="N33">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="O33">
+        <v>5.5</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
@@ -3711,46 +3807,43 @@
         <v>46090</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>37.5</v>
+        <v>7.6</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="E34">
-        <v>11.4</v>
+        <v>5</v>
       </c>
       <c r="F34">
-        <v>11.2</v>
+        <v>24.8</v>
       </c>
       <c r="G34">
-        <v>17.2</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>12.2</v>
+        <v>6.2</v>
       </c>
       <c r="I34">
-        <v>22.9</v>
+        <v>1.8</v>
       </c>
       <c r="J34">
-        <v>20.5</v>
+        <v>1</v>
       </c>
       <c r="K34">
-        <v>2</v>
+        <v>34.4</v>
       </c>
       <c r="L34">
-        <v>15.5</v>
+        <v>13.2</v>
       </c>
       <c r="M34">
-        <v>23.9</v>
+        <v>1.5</v>
       </c>
       <c r="N34">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="O34">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
@@ -3758,43 +3851,55 @@
         <v>46090</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C35">
-        <v>7.6</v>
+        <v>43.7</v>
       </c>
       <c r="D35">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>26.6</v>
       </c>
       <c r="F35">
-        <v>24.8</v>
+        <v>16.8</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="H35">
-        <v>6.2</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I35">
-        <v>1.8</v>
+        <v>44.6</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>26.7</v>
       </c>
       <c r="K35">
-        <v>34.4</v>
+        <v>29.9</v>
       </c>
       <c r="L35">
-        <v>13.2</v>
+        <v>36.9</v>
       </c>
       <c r="M35">
-        <v>1.5</v>
+        <v>26.7</v>
       </c>
       <c r="N35">
-        <v>6.5</v>
+        <v>26.9</v>
+      </c>
+      <c r="O35">
+        <v>27.1</v>
+      </c>
+      <c r="P35">
+        <v>3.3</v>
+      </c>
+      <c r="Q35">
+        <v>2.9</v>
+      </c>
+      <c r="R35">
+        <v>2.4</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.2">
@@ -3802,55 +3907,37 @@
         <v>46090</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C36">
-        <v>43.7</v>
+        <v>45.7</v>
       </c>
       <c r="D36">
-        <v>5.9</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="E36">
-        <v>26.6</v>
+        <v>5.6</v>
       </c>
       <c r="F36">
-        <v>16.8</v>
+        <v>7</v>
       </c>
       <c r="G36">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="H36">
-        <v>4.5999999999999996</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I36">
-        <v>44.6</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="J36">
-        <v>26.7</v>
+        <v>22.6</v>
       </c>
       <c r="K36">
-        <v>29.9</v>
+        <v>9.1</v>
       </c>
       <c r="L36">
-        <v>36.9</v>
-      </c>
-      <c r="M36">
-        <v>26.7</v>
-      </c>
-      <c r="N36">
-        <v>26.9</v>
-      </c>
-      <c r="O36">
-        <v>27.1</v>
-      </c>
-      <c r="P36">
-        <v>3.3</v>
-      </c>
-      <c r="Q36">
-        <v>2.9</v>
-      </c>
-      <c r="R36">
-        <v>2.4</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.2">
@@ -3858,37 +3945,46 @@
         <v>46090</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>45.7</v>
+        <v>9</v>
       </c>
       <c r="D37">
-        <v>39.799999999999997</v>
+        <v>29.1</v>
       </c>
       <c r="E37">
-        <v>5.6</v>
+        <v>18.3</v>
       </c>
       <c r="F37">
+        <v>11.9</v>
+      </c>
+      <c r="G37">
+        <v>10.5</v>
+      </c>
+      <c r="H37">
+        <v>23.2</v>
+      </c>
+      <c r="I37">
+        <v>12.6</v>
+      </c>
+      <c r="J37">
+        <v>7.5</v>
+      </c>
+      <c r="K37">
+        <v>6.2</v>
+      </c>
+      <c r="L37">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M37">
         <v>7</v>
       </c>
-      <c r="G37">
-        <v>2.6</v>
-      </c>
-      <c r="H37">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="I37">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="J37">
-        <v>22.6</v>
-      </c>
-      <c r="K37">
-        <v>9.1</v>
-      </c>
-      <c r="L37">
-        <v>42.3</v>
+      <c r="N37">
+        <v>5.9</v>
+      </c>
+      <c r="O37">
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.2">
@@ -3896,46 +3992,58 @@
         <v>46090</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>31.8</v>
       </c>
       <c r="D38">
-        <v>29.1</v>
+        <v>17.8</v>
       </c>
       <c r="E38">
-        <v>18.3</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>11.9</v>
+        <v>3.5</v>
       </c>
       <c r="G38">
-        <v>10.5</v>
+        <v>3.4</v>
       </c>
       <c r="H38">
-        <v>23.2</v>
+        <v>1</v>
       </c>
       <c r="I38">
-        <v>12.6</v>
+        <v>2.1</v>
       </c>
       <c r="J38">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="K38">
-        <v>6.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L38">
-        <v>4.4000000000000004</v>
+        <v>3.4</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>11.6</v>
       </c>
       <c r="N38">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="O38">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="P38">
+        <v>23.5</v>
+      </c>
+      <c r="Q38">
+        <v>4</v>
+      </c>
+      <c r="R38">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="S38">
+        <v>1.6</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.2">
@@ -3943,58 +4051,37 @@
         <v>46090</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C39">
-        <v>31.8</v>
+        <v>42</v>
       </c>
       <c r="D39">
-        <v>17.8</v>
+        <v>4.3</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>11.9</v>
       </c>
       <c r="F39">
-        <v>3.5</v>
+        <v>11.2</v>
       </c>
       <c r="G39">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="I39">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J39">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="K39">
-        <v>2.2000000000000002</v>
+        <v>10.5</v>
       </c>
       <c r="L39">
-        <v>3.4</v>
-      </c>
-      <c r="M39">
-        <v>11.6</v>
-      </c>
-      <c r="N39">
-        <v>9.6</v>
-      </c>
-      <c r="O39">
-        <v>5</v>
-      </c>
-      <c r="P39">
-        <v>23.5</v>
-      </c>
-      <c r="Q39">
-        <v>4</v>
-      </c>
-      <c r="R39">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="S39">
-        <v>1.6</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.2">
@@ -4002,95 +4089,37 @@
         <v>46090</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C40">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D40">
-        <v>4.3</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E40">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="F40">
-        <v>11.2</v>
+        <v>1.5</v>
       </c>
       <c r="G40">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="H40">
-        <v>4.5999999999999996</v>
+        <v>15</v>
       </c>
       <c r="I40">
-        <v>5.5</v>
+        <v>13.7</v>
       </c>
       <c r="J40">
-        <v>42</v>
-      </c>
-      <c r="K40">
-        <v>10.5</v>
-      </c>
-      <c r="L40">
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41">
-        <v>77.2</v>
-      </c>
-      <c r="D41">
-        <v>38</v>
-      </c>
-      <c r="E41">
-        <v>5.6</v>
-      </c>
-      <c r="F41">
-        <v>35.4</v>
-      </c>
-      <c r="G41">
-        <v>16.2</v>
-      </c>
-      <c r="H41">
-        <v>53.6</v>
-      </c>
-      <c r="I41">
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42">
-        <v>9</v>
-      </c>
-      <c r="D42">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E42">
-        <v>12.4</v>
-      </c>
-      <c r="F42">
-        <v>1.5</v>
-      </c>
-      <c r="G42">
-        <v>3.6</v>
-      </c>
-      <c r="H42">
-        <v>15</v>
-      </c>
-      <c r="I42">
-        <v>13.7</v>
-      </c>
-      <c r="J42">
         <v>4.4000000000000004</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -4118,11 +4147,11 @@
       </c>
       <c r="B2">
         <f>COUNTA('D3 3 9 26'!B2:B1048576)</f>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <f>COUNTA('D3 3 9 26'!C:C)</f>
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -6642,6 +6671,469 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28719112-2717-F844-B79E-E5F05D22F175}">
+  <dimension ref="A1:O40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="6.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.83203125" style="2"/>
+    <col min="5" max="13" width="5.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="15">
+        <v>46118</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="15">
+        <v>46118</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>51.8</v>
+      </c>
+      <c r="E3" s="2">
+        <v>41.1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>16.7</v>
+      </c>
+      <c r="H3" s="2">
+        <v>63.2</v>
+      </c>
+      <c r="I3" s="2">
+        <v>33.1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="15">
+        <v>46118</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>34.5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="F4" s="2">
+        <v>33.4</v>
+      </c>
+      <c r="O4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="15">
+        <v>46118</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="F5" s="2">
+        <v>30.6</v>
+      </c>
+      <c r="G5" s="2">
+        <v>34.200000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
+        <v>46118</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F6" s="2">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="G6" s="2">
+        <v>30.7</v>
+      </c>
+      <c r="H6" s="2">
+        <v>22.4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="15">
+        <v>46118</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>52.8</v>
+      </c>
+      <c r="E7" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="F7" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="G7" s="2">
+        <v>19.3</v>
+      </c>
+      <c r="H7" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.5</v>
+      </c>
+      <c r="J7" s="2">
+        <v>33</v>
+      </c>
+      <c r="K7" s="2">
+        <v>49.8</v>
+      </c>
+      <c r="L7" s="2">
+        <v>45.8</v>
+      </c>
+      <c r="M7" s="2">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="15">
+        <v>46118</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="E8" s="2">
+        <v>53.6</v>
+      </c>
+      <c r="F8" s="2">
+        <v>28.9</v>
+      </c>
+      <c r="G8" s="2">
+        <v>34.6</v>
+      </c>
+      <c r="O8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="15">
+        <v>46118</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>78.2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>94.6</v>
+      </c>
+      <c r="F9" s="2">
+        <v>86.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="15">
+        <v>46118</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>22.3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>25.3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>10.1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="I10" s="2">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="15">
+        <v>46118</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26E6E076-D55A-364B-966B-1A0A8B44E81C}">
   <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -6976,4 +7468,466 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0770AB5B-A91F-0E48-A8F6-268528AAE8A8}">
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="5" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="2">
+        <v>9.8300000000000002E-3</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1.0630000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3.0769999999999999E-2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>9.9900000000000006E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1.3780000000000001E-2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3.193E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3.431E-2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2.298E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.24E-2</v>
+      </c>
+      <c r="C6" s="2">
+        <v>6.3839999999999994E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5.2500000000000003E-3</v>
+      </c>
+      <c r="C7" s="2">
+        <v>9.5300000000000003E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2.392E-2</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3.2140000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2.9499999999999999E-3</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1.626E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1.73E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2.793E-2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>5.9909999999999998E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1.8849999999999999E-2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3.0339999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="2">
+        <v>4.1900000000000001E-3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>7.1700000000000002E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2">
+        <v>8.4899999999999993E-3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4.0480000000000002E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1.6840000000000001E-2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2.5250000000000002E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.661E-2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2.9260000000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1.332E-2</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3.4459999999999998E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1.223E-2</v>
+      </c>
+      <c r="C18" s="2">
+        <v>4.5749999999999999E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="2">
+        <v>7.9399999999999991E-3</v>
+      </c>
+      <c r="C19" s="2">
+        <v>4.7050000000000002E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2">
+        <v>3.9300000000000003E-3</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2.461E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2">
+        <v>3.8500000000000001E-3</v>
+      </c>
+      <c r="C21" s="2">
+        <v>2.3009999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1.7149999999999999E-2</v>
+      </c>
+      <c r="C22" s="2">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2.3359999999999999E-2</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2">
+        <v>9.2499999999999995E-3</v>
+      </c>
+      <c r="C24" s="2">
+        <v>8.0999999999999996E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="2">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2.3519999999999999E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="2">
+        <v>1.5869999999999999E-2</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2.2749999999999999E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="2">
+        <v>1.772E-2</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1.468E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="2">
+        <v>9.2399999999999999E-3</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1.0840000000000001E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="2">
+        <v>3.8500000000000001E-3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>3.9399999999999999E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="2">
+        <v>2.2179999999999998E-2</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1.584E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="2">
+        <v>1.772E-2</v>
+      </c>
+      <c r="C32" s="2">
+        <v>4.1309999999999999E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="2">
+        <v>2.4219999999999998E-2</v>
+      </c>
+      <c r="C33" s="2">
+        <v>4.6600000000000001E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="2">
+        <v>2.2370000000000001E-2</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2">
+        <v>1.457E-2</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2.7310000000000001E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="2">
+        <v>2.8320000000000001E-2</v>
+      </c>
+      <c r="C36" s="2">
+        <v>5.1399999999999996E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="2">
+        <v>1.74E-3</v>
+      </c>
+      <c r="C37" s="2">
+        <v>3.4250000000000003E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="2">
+        <v>4.2770000000000002E-2</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="2">
+        <v>1.298E-2</v>
+      </c>
+      <c r="C39" s="2">
+        <v>2.189E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B40" s="2">
+        <v>3.7200000000000002E-3</v>
+      </c>
+      <c r="C40" s="2">
+        <v>4.8390000000000002E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data_in/all_height_data.xlsx
+++ b/data_in/all_height_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacksonstrand/Documents/GitHub/Linaria_specProj/data_in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BAE643-D873-8E42-94FA-BB86B57D4BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A599D2E-4C4E-DE4A-99FE-8A0E4F0C7C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="1600" windowWidth="30240" windowHeight="18980" activeTab="8" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="9" xr2:uid="{8DE00727-C8D7-6A48-9276-98A4664605B4}"/>
   </bookViews>
   <sheets>
     <sheet name="D1 3 2 26" sheetId="2" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="D6 4 6 26" sheetId="9" r:id="rId7"/>
     <sheet name="meta_data" sheetId="8" r:id="rId8"/>
     <sheet name="weights" sheetId="10" r:id="rId9"/>
+    <sheet name="dry" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="105">
   <si>
     <t>lc1</t>
   </si>
@@ -350,13 +351,22 @@
   </si>
   <si>
     <t>dry_side</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>side</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -368,6 +378,13 @@
       <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -459,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -504,11 +521,22 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1616,6 +1644,462 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4339545-200C-8F4D-8121-EFC023484D1A}">
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3">
+        <v>6.45E-3</v>
+      </c>
+      <c r="C3">
+        <v>4.9199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>4.0699999999999998E-3</v>
+      </c>
+      <c r="C4">
+        <v>9.3699999999999999E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>2.8700000000000002E-3</v>
+      </c>
+      <c r="C5">
+        <v>4.3400000000000001E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6">
+        <v>8.5999999999999998E-4</v>
+      </c>
+      <c r="C6">
+        <v>1.1100000000000001E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>3.7599999999999999E-3</v>
+      </c>
+      <c r="C7">
+        <v>5.8300000000000001E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>1.8E-3</v>
+      </c>
+      <c r="C8">
+        <v>8.9300000000000004E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>3.9899999999999996E-3</v>
+      </c>
+      <c r="C9">
+        <v>5.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>2.7899999999999999E-3</v>
+      </c>
+      <c r="C10">
+        <v>1.042E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11">
+        <v>1.074E-2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>1.0399999999999999E-3</v>
+      </c>
+      <c r="C12">
+        <v>1.3600000000000001E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>2.0200000000000001E-3</v>
+      </c>
+      <c r="C13">
+        <v>1.1820000000000001E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>6.3499999999999997E-3</v>
+      </c>
+      <c r="C14">
+        <v>1.2099999999999999E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="C15">
+        <v>1.4420000000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16">
+        <v>3.2100000000000002E-3</v>
+      </c>
+      <c r="C16">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17">
+        <v>4.0200000000000001E-3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18">
+        <v>2.0100000000000001E-3</v>
+      </c>
+      <c r="C18">
+        <v>6.0299999999999998E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19">
+        <v>5.1799999999999997E-3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20">
+        <v>3.81E-3</v>
+      </c>
+      <c r="C20">
+        <v>1.07E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21">
+        <v>5.0299999999999997E-3</v>
+      </c>
+      <c r="C21">
+        <v>7.0600000000000003E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22">
+        <v>6.7200000000000003E-3</v>
+      </c>
+      <c r="C22">
+        <v>7.9500000000000005E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23">
+        <v>3.0500000000000002E-3</v>
+      </c>
+      <c r="C23">
+        <v>6.62E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24">
+        <v>5.4799999999999996E-3</v>
+      </c>
+      <c r="C24">
+        <v>1.2199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>6.4200000000000004E-3</v>
+      </c>
+      <c r="C25">
+        <v>1.16E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>3.29E-3</v>
+      </c>
+      <c r="C26">
+        <v>8.0499999999999999E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>2.5300000000000001E-3</v>
+      </c>
+      <c r="C27">
+        <v>1.338E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="C28">
+        <v>6.3000000000000003E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>4.1599999999999996E-3</v>
+      </c>
+      <c r="C29">
+        <v>2.81E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30">
+        <v>3.0200000000000001E-3</v>
+      </c>
+      <c r="C30">
+        <v>5.3200000000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>5.0699999999999999E-3</v>
+      </c>
+      <c r="C31">
+        <v>2.9199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32">
+        <v>1E-3</v>
+      </c>
+      <c r="C32">
+        <v>1.172E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33">
+        <v>5.5000000000000003E-4</v>
+      </c>
+      <c r="C33">
+        <v>7.2300000000000003E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34">
+        <v>1.74E-3</v>
+      </c>
+      <c r="C34">
+        <v>2.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35">
+        <v>7.7999999999999999E-4</v>
+      </c>
+      <c r="C35">
+        <v>2.14E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36">
+        <v>5.2999999999999998E-4</v>
+      </c>
+      <c r="C36">
+        <v>4.5500000000000002E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37">
+        <v>7.9000000000000001E-4</v>
+      </c>
+      <c r="C37">
+        <v>4.6699999999999997E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38">
+        <v>5.2999999999999998E-4</v>
+      </c>
+      <c r="C38">
+        <v>3.0899999999999999E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39">
+        <v>1.8799999999999999E-3</v>
+      </c>
+      <c r="C39">
+        <v>2.7999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40">
+        <v>1.3600000000000001E-3</v>
+      </c>
+      <c r="C40">
+        <v>1.8400000000000001E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C40">
+    <sortCondition ref="A2:A40"/>
+  </sortState>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E938CE3-B565-C14E-B603-EA123DBD5CB3}">
   <dimension ref="A1:T78"/>
@@ -4118,7 +4602,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7127,7 +7611,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7926,7 +8410,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
